--- a/data/trans_orig/CAGE-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265479</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>272086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,44 +1092,44 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>259850</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>255857</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>260838</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>259850</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>256275</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>260838</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>512</t>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>525128</t>
+          <t>524323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>532879</t>
+          <t>532889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>479324</t>
+          <t>479748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>490126</t>
+          <t>490058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>983863</t>
+          <t>983549</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>994162</t>
+          <t>994068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>345090</t>
+          <t>344778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>356636</t>
+          <t>356629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>363472</t>
+          <t>361584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>713654</t>
+          <t>713089</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>727110</t>
+          <t>726689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>198431</t>
+          <t>198760</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>199402</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>400740</t>
+          <t>402624</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>259866</t>
+          <t>259774</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>271093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>535234</t>
+          <t>537245</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>547230</t>
+          <t>547925</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>606615</t>
+          <t>607752</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>614177</t>
+          <t>614180</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1245624</t>
+          <t>1245464</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1252396</t>
+          <t>1252397</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>735038</t>
+          <t>734822</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>742907</t>
+          <t>742914</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>776106</t>
+          <t>776384</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1515733</t>
+          <t>1515289</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1525353</t>
+          <t>1525152</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5644,77 +5644,77 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -6090,12 +6090,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260852</t>
+          <t>261528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279259</t>
+          <t>279345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>281983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>545466</t>
+          <t>546573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>566854</t>
+          <t>566850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>484061</t>
+          <t>483892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>499790</t>
+          <t>499728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1007112</t>
+          <t>1008149</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1024075</t>
+          <t>1023197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>335428</t>
+          <t>336099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>659069</t>
+          <t>661100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>368928</t>
+          <t>369376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>759217</t>
+          <t>757810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -8592,12 +8592,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -8705,12 +8705,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>200014</t>
+          <t>199865</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>210269</t>
+          <t>210143</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>419235</t>
+          <t>418638</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>429569</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>268706</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>548712</t>
+          <t>548715</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -9730,12 +9730,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>641154</t>
+          <t>640910</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>656343</t>
+          <t>656868</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>687029</t>
+          <t>687248</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1332173</t>
+          <t>1332857</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1348692</t>
+          <t>1348660</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>756211</t>
+          <t>755561</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>773907</t>
+          <t>773023</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>818867</t>
+          <t>819837</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1578630</t>
+          <t>1579656</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1596573</t>
+          <t>1596978</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>28378</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56191</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -11560,12 +11560,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269315</t>
+          <t>267757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285438</t>
+          <t>285614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274268</t>
+          <t>274036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286029</t>
+          <t>285973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549848</t>
+          <t>548983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>569341</t>
+          <t>568906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -12242,12 +12242,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>491662</t>
+          <t>492710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>501456</t>
+          <t>501464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>516369</t>
+          <t>516760</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1013534</t>
+          <t>1013542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1023572</t>
+          <t>1023515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315061</t>
+          <t>313297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>650520</t>
+          <t>650724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>363117</t>
+          <t>362111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>749641</t>
+          <t>750879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -14062,12 +14062,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>203649</t>
+          <t>203553</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>210287</t>
+          <t>210286</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>422090</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>428874</t>
+          <t>428865</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>256362</t>
+          <t>256460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>267544</t>
+          <t>268350</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14701,12 +14701,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>527721</t>
+          <t>528633</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>535335</t>
+          <t>535348</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15087,12 +15087,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>25081</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -15200,12 +15200,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>627810</t>
+          <t>627830</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>646437</t>
+          <t>646661</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>679019</t>
+          <t>678976</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>689160</t>
+          <t>689202</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1312436</t>
+          <t>1312573</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1333540</t>
+          <t>1333866</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15656,12 +15656,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>766533</t>
+          <t>766501</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>776687</t>
+          <t>776646</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>819094</t>
+          <t>818471</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1589906</t>
+          <t>1590404</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1601615</t>
+          <t>1601685</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16225,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -16373,12 +16373,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -16922,12 +16922,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -16992,12 +16992,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -17025,32 +17025,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17095,22 +17095,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -17138,32 +17138,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>164979</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162903</t>
+          <t>158070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177605</t>
+          <t>168608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -17208,32 +17208,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>264247</t>
+          <t>262210</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>254289</t>
+          <t>254469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>268982</t>
+          <t>265831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -17251,17 +17251,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -17286,17 +17286,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -17321,17 +17321,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -17820,17 +17820,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -17890,17 +17890,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -17937,32 +17937,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -17982,12 +17982,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -18007,32 +18007,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -18050,32 +18050,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18120,32 +18120,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -18163,32 +18163,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>644</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -18208,12 +18208,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -18233,32 +18233,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -18276,67 +18276,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176061</t>
+          <t>176240</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169179</t>
+          <t>169190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180564</t>
+          <t>181432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>87498</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>84810</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>88792</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>95,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>85385</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89826</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18346,32 +18346,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>264650</t>
+          <t>263737</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257642</t>
+          <t>255380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269224</t>
+          <t>268809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -18389,17 +18389,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -18424,17 +18424,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18459,17 +18459,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -18516,12 +18516,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -18551,12 +18551,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18576,32 +18576,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -18742,12 +18742,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -18812,12 +18812,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -18845,32 +18845,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>174979</t>
+          <t>200212</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170707</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176760</t>
+          <t>201961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -18880,27 +18880,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123443</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121324</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -18915,27 +18915,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>298422</t>
+          <t>337599</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>294361</t>
+          <t>333057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300774</t>
+          <t>339831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -18958,17 +18958,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18993,17 +18993,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -19028,17 +19028,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -19120,12 +19120,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -19155,12 +19155,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -19449,27 +19449,27 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -19484,27 +19484,27 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -19527,17 +19527,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19562,17 +19562,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19597,17 +19597,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19644,32 +19644,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19679,32 +19679,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19714,22 +19714,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>590</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -19767,12 +19767,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>590</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>815</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -19880,12 +19880,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>815</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -19950,12 +19950,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -19983,32 +19983,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>160512</t>
+          <t>158668</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>155678</t>
+          <t>153943</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>163380</t>
+          <t>161399</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -20018,32 +20018,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>95963</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20053,22 +20053,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>254716</t>
+          <t>254631</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>249374</t>
+          <t>249087</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>258402</t>
+          <t>258037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -20096,17 +20096,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20131,17 +20131,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20166,17 +20166,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20213,22 +20213,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -20248,32 +20248,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -20283,32 +20283,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -20326,32 +20326,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20361,32 +20361,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20396,32 +20396,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -20439,32 +20439,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -20484,12 +20484,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20509,32 +20509,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -20552,32 +20552,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>298714</t>
+          <t>335212</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>323565</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>303237</t>
+          <t>342119</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20587,32 +20587,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>392747</t>
+          <t>223987</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>381130</t>
+          <t>213478</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>398844</t>
+          <t>229809</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20622,32 +20622,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>691461</t>
+          <t>559198</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>678800</t>
+          <t>545460</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>568166</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -20665,17 +20665,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20700,17 +20700,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20735,17 +20735,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -20905,12 +20905,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -20940,12 +20940,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -21018,12 +21018,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>756</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -21053,12 +21053,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -21088,12 +21088,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -21121,102 +21121,102 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>309214</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>267033</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>275496</t>
+          <t>312085</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>112605</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>108770</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>114166</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>421821</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>415639</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>425459</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>97709</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>94757</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>99101</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>370615</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>364905</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>373328</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -21234,17 +21234,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -21269,17 +21269,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -21304,17 +21304,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -21351,22 +21351,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21386,32 +21386,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21421,32 +21421,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -21464,32 +21464,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21499,32 +21499,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21534,32 +21534,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -21577,32 +21577,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>29136</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21612,32 +21612,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21647,32 +21647,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -21690,32 +21690,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21725,32 +21725,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21760,32 +21760,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -21803,17 +21803,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -21838,17 +21838,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -21873,17 +21873,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
